--- a/results/0916-all/豫皖鄂平原山地农林区/tech_selected_summary.xlsx
+++ b/results/0916-all/豫皖鄂平原山地农林区/tech_selected_summary.xlsx
@@ -145,241 +145,241 @@
     <t>镇平县</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>技术25</t>
-  </si>
-  <si>
-    <t>技术26</t>
-  </si>
-  <si>
-    <t>技术27</t>
-  </si>
-  <si>
-    <t>技术28</t>
-  </si>
-  <si>
-    <t>技术29</t>
-  </si>
-  <si>
-    <t>技术30</t>
-  </si>
-  <si>
-    <t>技术31</t>
-  </si>
-  <si>
-    <t>技术32</t>
-  </si>
-  <si>
-    <t>技术33</t>
-  </si>
-  <si>
-    <t>技术34</t>
-  </si>
-  <si>
-    <t>技术35</t>
-  </si>
-  <si>
-    <t>技术36</t>
-  </si>
-  <si>
-    <t>技术37</t>
-  </si>
-  <si>
-    <t>技术38</t>
-  </si>
-  <si>
-    <t>技术39</t>
-  </si>
-  <si>
-    <t>技术40</t>
-  </si>
-  <si>
-    <t>技术41</t>
-  </si>
-  <si>
-    <t>技术42</t>
-  </si>
-  <si>
-    <t>技术43</t>
-  </si>
-  <si>
-    <t>技术44</t>
-  </si>
-  <si>
-    <t>技术45</t>
-  </si>
-  <si>
-    <t>技术46</t>
-  </si>
-  <si>
-    <t>技术47</t>
-  </si>
-  <si>
-    <t>技术48</t>
-  </si>
-  <si>
-    <t>技术49</t>
-  </si>
-  <si>
-    <t>技术50</t>
-  </si>
-  <si>
-    <t>技术51</t>
-  </si>
-  <si>
-    <t>技术52</t>
-  </si>
-  <si>
-    <t>技术53</t>
-  </si>
-  <si>
-    <t>技术54</t>
-  </si>
-  <si>
-    <t>技术55</t>
-  </si>
-  <si>
-    <t>技术56</t>
-  </si>
-  <si>
-    <t>技术57</t>
-  </si>
-  <si>
-    <t>技术58</t>
-  </si>
-  <si>
-    <t>技术59</t>
-  </si>
-  <si>
-    <t>技术60</t>
-  </si>
-  <si>
-    <t>技术61</t>
-  </si>
-  <si>
-    <t>技术62</t>
-  </si>
-  <si>
-    <t>技术63</t>
-  </si>
-  <si>
-    <t>技术64</t>
-  </si>
-  <si>
-    <t>技术65</t>
-  </si>
-  <si>
-    <t>技术66</t>
-  </si>
-  <si>
-    <t>技术67</t>
-  </si>
-  <si>
-    <t>技术68</t>
-  </si>
-  <si>
-    <t>技术69</t>
-  </si>
-  <si>
-    <t>技术70</t>
-  </si>
-  <si>
-    <t>技术71</t>
-  </si>
-  <si>
-    <t>技术72</t>
-  </si>
-  <si>
-    <t>技术73</t>
-  </si>
-  <si>
-    <t>技术74</t>
-  </si>
-  <si>
-    <t>技术75</t>
-  </si>
-  <si>
-    <t>技术76</t>
-  </si>
-  <si>
-    <t>技术77</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Tech25</t>
+  </si>
+  <si>
+    <t>Tech26</t>
+  </si>
+  <si>
+    <t>Tech27</t>
+  </si>
+  <si>
+    <t>Tech28</t>
+  </si>
+  <si>
+    <t>Tech29</t>
+  </si>
+  <si>
+    <t>Tech30</t>
+  </si>
+  <si>
+    <t>Tech31</t>
+  </si>
+  <si>
+    <t>Tech32</t>
+  </si>
+  <si>
+    <t>Tech33</t>
+  </si>
+  <si>
+    <t>Tech34</t>
+  </si>
+  <si>
+    <t>Tech35</t>
+  </si>
+  <si>
+    <t>Tech36</t>
+  </si>
+  <si>
+    <t>Tech37</t>
+  </si>
+  <si>
+    <t>Tech38</t>
+  </si>
+  <si>
+    <t>Tech39</t>
+  </si>
+  <si>
+    <t>Tech40</t>
+  </si>
+  <si>
+    <t>Tech41</t>
+  </si>
+  <si>
+    <t>Tech42</t>
+  </si>
+  <si>
+    <t>Tech43</t>
+  </si>
+  <si>
+    <t>Tech44</t>
+  </si>
+  <si>
+    <t>Tech45</t>
+  </si>
+  <si>
+    <t>Tech46</t>
+  </si>
+  <si>
+    <t>Tech47</t>
+  </si>
+  <si>
+    <t>Tech48</t>
+  </si>
+  <si>
+    <t>Tech49</t>
+  </si>
+  <si>
+    <t>Tech50</t>
+  </si>
+  <si>
+    <t>Tech51</t>
+  </si>
+  <si>
+    <t>Tech52</t>
+  </si>
+  <si>
+    <t>Tech53</t>
+  </si>
+  <si>
+    <t>Tech54</t>
+  </si>
+  <si>
+    <t>Tech55</t>
+  </si>
+  <si>
+    <t>Tech56</t>
+  </si>
+  <si>
+    <t>Tech57</t>
+  </si>
+  <si>
+    <t>Tech58</t>
+  </si>
+  <si>
+    <t>Tech59</t>
+  </si>
+  <si>
+    <t>Tech60</t>
+  </si>
+  <si>
+    <t>Tech61</t>
+  </si>
+  <si>
+    <t>Tech62</t>
+  </si>
+  <si>
+    <t>Tech63</t>
+  </si>
+  <si>
+    <t>Tech64</t>
+  </si>
+  <si>
+    <t>Tech65</t>
+  </si>
+  <si>
+    <t>Tech66</t>
+  </si>
+  <si>
+    <t>Tech67</t>
+  </si>
+  <si>
+    <t>Tech68</t>
+  </si>
+  <si>
+    <t>Tech69</t>
+  </si>
+  <si>
+    <t>Tech70</t>
+  </si>
+  <si>
+    <t>Tech71</t>
+  </si>
+  <si>
+    <t>Tech72</t>
+  </si>
+  <si>
+    <t>Tech73</t>
+  </si>
+  <si>
+    <t>Tech74</t>
+  </si>
+  <si>
+    <t>Tech75</t>
+  </si>
+  <si>
+    <t>Tech76</t>
+  </si>
+  <si>
+    <t>Tech77</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
@@ -475,7 +475,7 @@
     <t>irrigation (drip irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 183015117.49</t>
+    <t>183015117.49</t>
   </si>
   <si>
     <t>Increasing byproduct_beef cattle</t>
@@ -508,7 +508,7 @@
     <t>4R(Right type)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 182810259.73</t>
+    <t>182810259.73</t>
   </si>
   <si>
     <t>Increasing feeding level_sheep &amp; goat</t>
@@ -562,7 +562,7 @@
     <t>irrigation (drip irrigation)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 977493556.27</t>
+    <t>977493556.27</t>
   </si>
   <si>
     <t>chemical amendments_pig</t>
@@ -589,13 +589,13 @@
     <t>irrigation (water-saving irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 75455836.95</t>
+    <t>75455836.95</t>
   </si>
   <si>
     <t>nitrification inhibitor_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 463751724.28</t>
+    <t>463751724.28</t>
   </si>
   <si>
     <t>Bioflilter_poultry</t>
@@ -616,13 +616,13 @@
     <t>irrigation (water-saving irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 1336472731.96</t>
-  </si>
-  <si>
-    <t>总经济成本: 77959448.95</t>
-  </si>
-  <si>
-    <t>总经济成本: 174067873.37</t>
+    <t>1336472731.96</t>
+  </si>
+  <si>
+    <t>77959448.95</t>
+  </si>
+  <si>
+    <t>174067873.37</t>
   </si>
   <si>
     <t>Frequent removal_sheep&amp;goat</t>
@@ -634,16 +634,16 @@
     <t>cover crop (mix)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 174825992.78</t>
-  </si>
-  <si>
-    <t>总经济成本: 642184905.04</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 71413034.58</t>
+    <t>174825992.78</t>
+  </si>
+  <si>
+    <t>642184905.04</t>
+  </si>
+  <si>
+    <t>0.00</t>
+  </si>
+  <si>
+    <t>71413034.58</t>
   </si>
   <si>
     <t>manure（high）≥70%_rice</t>
@@ -652,7 +652,7 @@
     <t>irrigation (AWD irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 269844950.06</t>
+    <t>269844950.06</t>
   </si>
   <si>
     <t>Biochar_dairy</t>
@@ -667,49 +667,49 @@
     <t>Mixture additives _dairy</t>
   </si>
   <si>
-    <t>总经济成本: 349270911.30</t>
+    <t>349270911.30</t>
   </si>
   <si>
     <t>Feedstock adjustment_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 335112123.49</t>
-  </si>
-  <si>
-    <t>总经济成本: 27929566.62</t>
-  </si>
-  <si>
-    <t>总经济成本: 153637151.08</t>
+    <t>335112123.49</t>
+  </si>
+  <si>
+    <t>27929566.62</t>
+  </si>
+  <si>
+    <t>153637151.08</t>
   </si>
   <si>
     <t>residue rerention_maize</t>
   </si>
   <si>
-    <t>总经济成本: 246442010.19</t>
+    <t>246442010.19</t>
   </si>
   <si>
     <t>biochar_rice</t>
   </si>
   <si>
-    <t>总经济成本: 541098951.75</t>
-  </si>
-  <si>
-    <t>总经济成本: 23398599.96</t>
-  </si>
-  <si>
-    <t>总经济成本: 379263084.69</t>
+    <t>541098951.75</t>
+  </si>
+  <si>
+    <t>23398599.96</t>
+  </si>
+  <si>
+    <t>379263084.69</t>
   </si>
   <si>
     <t>Nitrocompounds_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 89366289.51</t>
+    <t>89366289.51</t>
   </si>
   <si>
     <t>tillage management (zero tillage)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 263332808.69</t>
+    <t>263332808.69</t>
   </si>
   <si>
     <t>Low protein diet_Pig</t>
@@ -739,16 +739,16 @@
     <t>4R(Right place)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 1470178682.10</t>
+    <t>1470178682.10</t>
   </si>
   <si>
     <t>tillage management (zero tillage)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 334927380.21</t>
-  </si>
-  <si>
-    <t>总经济成本: 735452530.60</t>
+    <t>334927380.21</t>
+  </si>
+  <si>
+    <t>735452530.60</t>
   </si>
   <si>
     <t>Zeolite_pig</t>
@@ -757,25 +757,25 @@
     <t>irrigation (water-saving irrigation)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 261649917.97</t>
+    <t>261649917.97</t>
   </si>
   <si>
     <t>cover crop (non-leguminous)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 383985675.79</t>
-  </si>
-  <si>
-    <t>总经济成本: 444953706.89</t>
-  </si>
-  <si>
-    <t>总经济成本: 385600175.35</t>
+    <t>383985675.79</t>
+  </si>
+  <si>
+    <t>444953706.89</t>
+  </si>
+  <si>
+    <t>385600175.35</t>
   </si>
   <si>
     <t>rolller press_pig</t>
   </si>
   <si>
-    <t>总经济成本: 1109047244.51</t>
+    <t>1109047244.51</t>
   </si>
   <si>
     <t>Screw press_pig</t>
@@ -802,31 +802,31 @@
     <t>irrigation (water-saving irrigation)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 859927979.95</t>
-  </si>
-  <si>
-    <t>总经济成本: 6523779.27</t>
-  </si>
-  <si>
-    <t>总经济成本: 463804631.76</t>
-  </si>
-  <si>
-    <t>总经济成本: 691336710.49</t>
+    <t>859927979.95</t>
+  </si>
+  <si>
+    <t>6523779.27</t>
+  </si>
+  <si>
+    <t>463804631.76</t>
+  </si>
+  <si>
+    <t>691336710.49</t>
   </si>
   <si>
     <t>Decreasing grass maturity_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 81069483.98</t>
-  </si>
-  <si>
-    <t>总经济成本: 113470765.70</t>
-  </si>
-  <si>
-    <t>总经济成本: 1090203301.43</t>
-  </si>
-  <si>
-    <t>总经济成本: 85576866.76</t>
+    <t>81069483.98</t>
+  </si>
+  <si>
+    <t>113470765.70</t>
+  </si>
+  <si>
+    <t>1090203301.43</t>
+  </si>
+  <si>
+    <t>85576866.76</t>
   </si>
 </sst>
 </file>
